--- a/Masters.xlsx
+++ b/Masters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DrawingLight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B067B340-B434-4D04-A84B-FE487C6D6A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10FFDE6-0943-4D8F-94F5-2D6E46D6E3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C60EF2B-C175-467E-B01A-F884B8007B03}"/>
   </bookViews>
@@ -14520,12 +14520,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="177"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14571,6 +14579,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -14644,8 +14658,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -14653,31 +14668,32 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{3FC870FA-F9F3-4984-8806-016659A87DD3}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{0BD39C17-9A10-441C-A371-0243211B22BE}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{A8BFF532-57E9-470B-BDF1-BFC17F072401}"/>
     <cellStyle name="Normal 5" xfId="4" xr:uid="{F39DA740-841B-41EF-A569-196732533C4D}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{97D63F24-31E8-41BB-9148-98E90EEBA609}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -14693,7 +14709,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -15014,6 +15030,7 @@
   <cols>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="143.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="75.5703125" customWidth="1"/>
   </cols>
   <sheetData>
